--- a/keydates/newdata_10082026/10082026_early_voting_data_WITHNOTES (1).xlsx
+++ b/keydates/newdata_10082026/10082026_early_voting_data_WITHNOTES (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://brennancenterny-my.sharepoint.com/personal/zhangj_brennan_law_nyu_edu/Documents/Documents/2026_midterms/keydates/newdata_10082026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_042D85090C6CC8E6966078651AAD65DC05169CEC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A81D5F6-75BB-B145-A6C5-3F1520365D32}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{BFCA26BD-F43D-FF42-BE4E-CCE79770791E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,20 @@
     <sheet name="Early Voting Daily Totals UPDAT" sheetId="2" r:id="rId2"/>
     <sheet name="Early Voting Daily Totals Data " sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1231,7 +1244,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1259,6 +1272,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1280,12 +1301,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1507,7 +1529,7 @@
   <dimension ref="A1:L51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="11" max="11" width="47" customWidth="1"/>
+    <col min="11" max="11" width="47" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1690,7 +1712,7 @@
       <c r="K5" s="2">
         <v>46300</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="5">
         <v>46328</v>
       </c>
     </row>
@@ -1728,7 +1750,7 @@
       <c r="K6" s="2">
         <v>46314</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6" s="5">
         <v>46328</v>
       </c>
     </row>
@@ -1798,7 +1820,7 @@
       <c r="J8" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="5">
         <v>46317</v>
       </c>
       <c r="L8" s="2">
@@ -1836,7 +1858,7 @@
       <c r="J9" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="5">
         <v>46321</v>
       </c>
       <c r="L9" s="3">
@@ -1874,7 +1896,7 @@
       <c r="J10" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="5">
         <v>46319</v>
       </c>
       <c r="L10" s="3">
@@ -1912,7 +1934,7 @@
       <c r="J11" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="K11" s="3">
+      <c r="K11" s="5">
         <v>46308</v>
       </c>
       <c r="L11" s="2">
@@ -1985,7 +2007,7 @@
       <c r="J13" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="K13" s="3">
+      <c r="K13" s="5">
         <v>46308</v>
       </c>
       <c r="L13" s="2">
@@ -2233,7 +2255,7 @@
       <c r="J20" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="5">
         <v>46300</v>
       </c>
       <c r="L20" s="2">
@@ -2411,7 +2433,7 @@
       <c r="K25" s="2">
         <v>46315</v>
       </c>
-      <c r="L25" s="3">
+      <c r="L25" s="5">
         <v>46328</v>
       </c>
     </row>
@@ -2446,7 +2468,7 @@
       <c r="J26" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K26" s="5">
         <v>46300</v>
       </c>
       <c r="L26" s="2">
@@ -2484,7 +2506,7 @@
       <c r="J27" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="K27" s="3">
+      <c r="K27" s="5">
         <v>46300</v>
       </c>
       <c r="L27" s="2">
@@ -2732,7 +2754,7 @@
       <c r="J34" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="K34" s="3">
+      <c r="K34" s="5">
         <v>46301</v>
       </c>
       <c r="L34" s="2">
@@ -2913,10 +2935,10 @@
       <c r="J39" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="K39" s="3">
+      <c r="K39" s="5">
         <v>46314</v>
       </c>
-      <c r="L39" s="3">
+      <c r="L39" s="5">
         <v>46326</v>
       </c>
     </row>
@@ -3059,7 +3081,7 @@
       <c r="K43" s="2">
         <v>46315</v>
       </c>
-      <c r="L43" s="3">
+      <c r="L43" s="5">
         <v>46325</v>
       </c>
     </row>
@@ -3132,7 +3154,7 @@
       <c r="J45" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="5">
         <v>46283</v>
       </c>
       <c r="L45" s="2">
@@ -3809,10 +3831,10 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3850,7 +3872,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>22</v>
       </c>
@@ -3887,8 +3909,12 @@
       <c r="L2" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M2">
+        <f>J2-K2-L2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>31</v>
       </c>
@@ -3919,8 +3945,12 @@
       <c r="L3" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M3">
+        <f>J3-K3-L3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>37</v>
       </c>
@@ -3954,8 +3984,12 @@
       <c r="L4" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M4">
+        <f t="shared" ref="M4:M49" si="0">J4-K4-L4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
         <v>40</v>
       </c>
@@ -3992,8 +4026,12 @@
       <c r="L5" s="1">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>49</v>
       </c>
@@ -4030,8 +4068,12 @@
       <c r="L6" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
         <v>55</v>
       </c>
@@ -4065,8 +4107,12 @@
       <c r="L7" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
         <v>61</v>
       </c>
@@ -4103,8 +4149,12 @@
       <c r="L8" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
         <v>68</v>
       </c>
@@ -4141,8 +4191,12 @@
       <c r="L9" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>75</v>
       </c>
@@ -4179,8 +4233,12 @@
       <c r="L10" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
         <v>82</v>
       </c>
@@ -4217,8 +4275,12 @@
       <c r="L11" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
         <v>89</v>
       </c>
@@ -4252,8 +4314,12 @@
       <c r="L12" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
         <v>96</v>
       </c>
@@ -4290,8 +4356,12 @@
       <c r="L13" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
         <v>103</v>
       </c>
@@ -4325,8 +4395,12 @@
       <c r="L14" s="1">
         <v>11</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
         <v>108</v>
       </c>
@@ -4360,8 +4434,12 @@
       <c r="L15" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
         <v>115</v>
       </c>
@@ -4395,8 +4473,12 @@
       <c r="L16" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
         <v>120</v>
       </c>
@@ -4430,8 +4512,12 @@
       <c r="L17" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
         <v>125</v>
       </c>
@@ -4465,8 +4551,12 @@
       <c r="L18" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
         <v>128</v>
       </c>
@@ -4500,8 +4590,12 @@
       <c r="L19" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
         <v>131</v>
       </c>
@@ -4538,8 +4632,12 @@
       <c r="L20" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
         <v>139</v>
       </c>
@@ -4573,8 +4671,12 @@
       <c r="L21" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
         <v>145</v>
       </c>
@@ -4608,8 +4710,12 @@
       <c r="L22" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
         <v>150</v>
       </c>
@@ -4643,8 +4749,12 @@
       <c r="L23" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
         <v>156</v>
       </c>
@@ -4678,8 +4788,12 @@
       <c r="L24" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M24">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
         <v>162</v>
       </c>
@@ -4713,8 +4827,12 @@
       <c r="L25" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="26" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
         <v>171</v>
       </c>
@@ -4751,8 +4869,12 @@
       <c r="L26" s="1">
         <v>9</v>
       </c>
-    </row>
-    <row r="27" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="1" t="s">
         <v>176</v>
       </c>
@@ -4789,8 +4911,12 @@
       <c r="L27" s="1">
         <v>9</v>
       </c>
-    </row>
-    <row r="28" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M27">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
         <v>184</v>
       </c>
@@ -4824,8 +4950,12 @@
       <c r="L28" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="29" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M28">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="1" t="s">
         <v>192</v>
       </c>
@@ -4859,8 +4989,12 @@
       <c r="L29" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M29">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="1" t="s">
         <v>199</v>
       </c>
@@ -4894,8 +5028,12 @@
       <c r="L30" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="31" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="1" t="s">
         <v>205</v>
       </c>
@@ -4929,8 +5067,12 @@
       <c r="L31" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
         <v>212</v>
       </c>
@@ -4964,8 +5106,12 @@
       <c r="L32" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
         <v>218</v>
       </c>
@@ -4999,8 +5145,12 @@
       <c r="L33" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M33">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
         <v>224</v>
       </c>
@@ -5037,8 +5187,12 @@
       <c r="L34" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="35" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
         <v>231</v>
       </c>
@@ -5072,8 +5226,12 @@
       <c r="L35" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
         <v>237</v>
       </c>
@@ -5110,8 +5268,12 @@
       <c r="L36" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="37" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
         <v>245</v>
       </c>
@@ -5145,8 +5307,12 @@
       <c r="L37" s="1">
         <v>13</v>
       </c>
-    </row>
-    <row r="38" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="1" t="s">
         <v>250</v>
       </c>
@@ -5180,8 +5346,12 @@
       <c r="L38" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="39" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M38">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="1" t="s">
         <v>253</v>
       </c>
@@ -5218,8 +5388,12 @@
       <c r="L39" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="1" t="s">
         <v>262</v>
       </c>
@@ -5253,8 +5427,12 @@
       <c r="L40" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="41" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M40">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="1" t="s">
         <v>268</v>
       </c>
@@ -5288,8 +5466,12 @@
       <c r="L41" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="42" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="1" t="s">
         <v>274</v>
       </c>
@@ -5323,8 +5505,12 @@
       <c r="L42" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M42">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="1" t="s">
         <v>280</v>
       </c>
@@ -5361,8 +5547,12 @@
       <c r="L43" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="44" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M43">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
         <v>288</v>
       </c>
@@ -5399,8 +5589,12 @@
       <c r="L44" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="45" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="1" t="s">
         <v>295</v>
       </c>
@@ -5437,8 +5631,12 @@
       <c r="L45" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="46" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M45">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="1" t="s">
         <v>303</v>
       </c>
@@ -5472,8 +5670,12 @@
       <c r="L46" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="47" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M46">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
         <v>308</v>
       </c>
@@ -5507,8 +5709,12 @@
       <c r="L47" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
         <v>315</v>
       </c>
@@ -5542,8 +5748,12 @@
       <c r="L48" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M48">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="1" t="s">
         <v>320</v>
       </c>
@@ -5576,6 +5786,10 @@
       </c>
       <c r="L49" s="1">
         <v>9</v>
+      </c>
+      <c r="M49">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
